--- a/MavenBook/src/test/resources/SalesInvoiceData.xlsx
+++ b/MavenBook/src/test/resources/SalesInvoiceData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="38">
   <si>
     <t>Customer Name</t>
   </si>
@@ -56,18 +56,6 @@
     <t>Others</t>
   </si>
   <si>
-    <t>Sales P1</t>
-  </si>
-  <si>
-    <t>Subinm</t>
-  </si>
-  <si>
-    <t>Red Pen</t>
-  </si>
-  <si>
-    <t>30-12-2025</t>
-  </si>
-  <si>
     <t>Tax</t>
   </si>
   <si>
@@ -92,28 +80,55 @@
     <t>termsx</t>
   </si>
   <si>
+    <t>Discount Type</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>1010-1</t>
+  </si>
+  <si>
+    <t>Joy</t>
+  </si>
+  <si>
     <t>SAVE AND APPROVE</t>
   </si>
   <si>
-    <t>special price</t>
-  </si>
-  <si>
-    <t>Discount Type</t>
-  </si>
-  <si>
-    <t>Discount</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>amount</t>
-  </si>
-  <si>
-    <t>27-12-2025</t>
-  </si>
-  <si>
-    <t>271225</t>
+    <t>FEB 1</t>
+  </si>
+  <si>
+    <t>Exclusive</t>
+  </si>
+  <si>
+    <t>1010-2</t>
+  </si>
+  <si>
+    <t>April three</t>
+  </si>
+  <si>
+    <t>1010-3</t>
+  </si>
+  <si>
+    <t>Notebook 100</t>
+  </si>
+  <si>
+    <t>Pencil</t>
+  </si>
+  <si>
+    <t>Coffe</t>
+  </si>
+  <si>
+    <t>April one two</t>
+  </si>
+  <si>
+    <t>1010-4</t>
   </si>
 </sst>
 </file>
@@ -519,7 +534,7 @@
     <col min="8" max="8" width="21.140625" style="8" customWidth="1"/>
     <col min="9" max="9" width="16.28515625" style="8" customWidth="1"/>
     <col min="10" max="10" width="20.5703125" style="8" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="27.42578125" style="8" customWidth="1"/>
     <col min="12" max="12" width="20.28515625" style="8" customWidth="1"/>
     <col min="13" max="13" width="15.85546875" style="8" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="8"/>
@@ -551,138 +566,380 @@
         <v>3</v>
       </c>
       <c r="I1" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>16</v>
-      </c>
       <c r="F2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>13</v>
-      </c>
       <c r="H2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="M2" t="s">
+      <c r="D6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="K3" s="9"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="K4" s="9"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="K5" s="9"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="K6" s="9"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="K7" s="9"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="K8" s="9"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="K9" s="9"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="K10" s="9"/>
+      <c r="B10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="K11" s="9"/>
+      <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="A12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="K13" s="9"/>
+      <c r="A13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M13"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14" s="9"/>
@@ -842,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.85546875" style="1" customWidth="1"/>
@@ -862,24 +1119,24 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E2">
         <v>10</v>
@@ -887,19 +1144,171 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E3">
         <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/MavenBook/src/test/resources/SalesInvoiceData.xlsx
+++ b/MavenBook/src/test/resources/SalesInvoiceData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="SalesInvoiceHeader" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="43">
   <si>
     <t>Customer Name</t>
   </si>
@@ -29,9 +29,6 @@
     <t>Subject</t>
   </si>
   <si>
-    <t>Test SI</t>
-  </si>
-  <si>
     <t>Sales Person</t>
   </si>
   <si>
@@ -71,71 +68,89 @@
     <t>Price List</t>
   </si>
   <si>
+    <t>notex</t>
+  </si>
+  <si>
+    <t>termsx</t>
+  </si>
+  <si>
+    <t>Discount Type</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>1010-1</t>
+  </si>
+  <si>
+    <t>SAVE AND APPROVE</t>
+  </si>
+  <si>
+    <t>Exclusive</t>
+  </si>
+  <si>
+    <t>VAT Registered</t>
+  </si>
+  <si>
+    <t>10-05-2026</t>
+  </si>
+  <si>
+    <t>Exc SI</t>
+  </si>
+  <si>
+    <t>Pear</t>
+  </si>
+  <si>
+    <t>1010-2</t>
+  </si>
+  <si>
+    <t>Inc SI</t>
+  </si>
+  <si>
     <t>Inclusive</t>
   </si>
   <si>
-    <t>notex</t>
-  </si>
-  <si>
-    <t>termsx</t>
-  </si>
-  <si>
-    <t>Discount Type</t>
-  </si>
-  <si>
-    <t>Discount</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>amount</t>
-  </si>
-  <si>
-    <t>1010-1</t>
-  </si>
-  <si>
-    <t>Joy</t>
-  </si>
-  <si>
-    <t>SAVE AND APPROVE</t>
-  </si>
-  <si>
-    <t>FEB 1</t>
-  </si>
-  <si>
-    <t>Exclusive</t>
-  </si>
-  <si>
-    <t>1010-2</t>
-  </si>
-  <si>
-    <t>April three</t>
+    <t>Gcc VAT Registered</t>
   </si>
   <si>
     <t>1010-3</t>
   </si>
   <si>
-    <t>Notebook 100</t>
-  </si>
-  <si>
-    <t>Pencil</t>
-  </si>
-  <si>
-    <t>Coffe</t>
-  </si>
-  <si>
-    <t>April one two</t>
-  </si>
-  <si>
     <t>1010-4</t>
+  </si>
+  <si>
+    <t>Gcc Non VAT Registered</t>
+  </si>
+  <si>
+    <t>1010-5</t>
+  </si>
+  <si>
+    <t>1010-6</t>
+  </si>
+  <si>
+    <t>Non Gcc</t>
+  </si>
+  <si>
+    <t>1010-7</t>
+  </si>
+  <si>
+    <t>1010-8</t>
+  </si>
+  <si>
+    <t>Non VAT Registered</t>
+  </si>
+  <si>
+    <t>1010-9</t>
+  </si>
+  <si>
+    <t>1010-10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +185,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -191,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -218,6 +240,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -522,10 +548,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" style="9" customWidth="1"/>
     <col min="2" max="2" width="16" style="8" customWidth="1"/>
     <col min="3" max="3" width="16" style="9" customWidth="1"/>
     <col min="4" max="4" width="16" style="8" customWidth="1"/>
@@ -545,401 +571,385 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>10</v>
-      </c>
       <c r="G1" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="L1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="M1" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>4</v>
-      </c>
       <c r="I2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>20</v>
-      </c>
       <c r="L2" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M2"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="D3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>29</v>
-      </c>
       <c r="J3" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M3"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>12</v>
-      </c>
       <c r="H4" s="8" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="I4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>4</v>
-      </c>
       <c r="I5" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M5"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>4</v>
-      </c>
       <c r="I6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>20</v>
-      </c>
       <c r="L6" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M6"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="J7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I7" s="9" t="s">
+      <c r="H8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="J7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="8" t="s">
+      <c r="I9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" s="9" t="s">
+      <c r="H10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="9" t="s">
+      <c r="I11" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>20</v>
-      </c>
       <c r="L11" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M11"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L12" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12"/>
+      <c r="B12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="K12" s="9"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M13"/>
+      <c r="B13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="K13" s="9"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14" s="9"/>
@@ -1008,28 +1018,24 @@
       <c r="B23" s="9"/>
       <c r="D23" s="9"/>
       <c r="F23" s="9"/>
-      <c r="I23" s="9"/>
       <c r="K23" s="9"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="9"/>
       <c r="D24" s="9"/>
       <c r="F24" s="9"/>
-      <c r="I24" s="9"/>
       <c r="K24" s="9"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="9"/>
       <c r="D25" s="9"/>
       <c r="F25" s="9"/>
-      <c r="I25" s="9"/>
       <c r="K25" s="9"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="9"/>
       <c r="D26" s="9"/>
       <c r="F26" s="9"/>
-      <c r="I26" s="9"/>
       <c r="K26" s="9"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
@@ -1066,30 +1072,6 @@
       <c r="B32" s="9"/>
       <c r="D32" s="9"/>
       <c r="F32" s="9"/>
-      <c r="K32" s="9"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="K33" s="9"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="K34" s="9"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="K35" s="9"/>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="F36" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1099,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.85546875" style="1" customWidth="1"/>
@@ -1119,197 +1101,142 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>28</v>
+      <c r="A6" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9">
-        <v>5</v>
-      </c>
-    </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10">
-        <v>5</v>
-      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MavenBook/src/test/resources/SalesInvoiceData.xlsx
+++ b/MavenBook/src/test/resources/SalesInvoiceData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SalesInvoiceHeader" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="48">
   <si>
     <t>Customer Name</t>
   </si>
@@ -68,6 +68,9 @@
     <t>Price List</t>
   </si>
   <si>
+    <t>Inclusive</t>
+  </si>
+  <si>
     <t>notex</t>
   </si>
   <si>
@@ -80,6 +83,12 @@
     <t>Discount</t>
   </si>
   <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
     <t>1010-1</t>
   </si>
   <si>
@@ -89,68 +98,74 @@
     <t>Exclusive</t>
   </si>
   <si>
-    <t>VAT Registered</t>
-  </si>
-  <si>
-    <t>10-05-2026</t>
+    <t>1010-2</t>
+  </si>
+  <si>
+    <t>1010-3</t>
+  </si>
+  <si>
+    <t>1010-4</t>
+  </si>
+  <si>
+    <t>1010-5</t>
+  </si>
+  <si>
+    <t>Service 1</t>
   </si>
   <si>
     <t>Exc SI</t>
   </si>
   <si>
-    <t>Pear</t>
-  </si>
-  <si>
-    <t>1010-2</t>
-  </si>
-  <si>
     <t>Inc SI</t>
   </si>
   <si>
-    <t>Inclusive</t>
-  </si>
-  <si>
-    <t>Gcc VAT Registered</t>
-  </si>
-  <si>
-    <t>1010-3</t>
-  </si>
-  <si>
-    <t>1010-4</t>
-  </si>
-  <si>
-    <t>Gcc Non VAT Registered</t>
-  </si>
-  <si>
-    <t>1010-5</t>
-  </si>
-  <si>
     <t>1010-6</t>
   </si>
   <si>
-    <t>Non Gcc</t>
-  </si>
-  <si>
     <t>1010-7</t>
   </si>
   <si>
     <t>1010-8</t>
   </si>
   <si>
-    <t>Non VAT Registered</t>
-  </si>
-  <si>
     <t>1010-9</t>
   </si>
   <si>
     <t>1010-10</t>
+  </si>
+  <si>
+    <t>Vat Reg Customer</t>
+  </si>
+  <si>
+    <t>CDName</t>
+  </si>
+  <si>
+    <t>Mr Abel Patriarch</t>
+  </si>
+  <si>
+    <t>Non GCC Customer OMR</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>25-08-2026</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>Non inv 1</t>
+  </si>
+  <si>
+    <t>Avokado</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,6 +207,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -201,7 +222,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -209,16 +230,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -240,8 +273,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -551,527 +597,527 @@
   <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" style="9" customWidth="1"/>
-    <col min="2" max="2" width="16" style="8" customWidth="1"/>
-    <col min="3" max="3" width="16" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16" style="8" customWidth="1"/>
-    <col min="5" max="5" width="16" style="9" customWidth="1"/>
-    <col min="6" max="7" width="16" style="8" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" style="8" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="20.5703125" style="8" customWidth="1"/>
-    <col min="11" max="11" width="27.42578125" style="8" customWidth="1"/>
-    <col min="12" max="12" width="20.28515625" style="8" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" style="8" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="1" width="22.7109375" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16" style="7" customWidth="1"/>
+    <col min="3" max="3" width="16" style="8" customWidth="1"/>
+    <col min="4" max="4" width="16" style="7" customWidth="1"/>
+    <col min="5" max="5" width="16" style="8" customWidth="1"/>
+    <col min="6" max="7" width="16" style="7" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="16.28515625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="20.5703125" style="7" customWidth="1"/>
+    <col min="11" max="11" width="27.42578125" style="7" customWidth="1"/>
+    <col min="12" max="12" width="20.28515625" style="7" customWidth="1"/>
+    <col min="13" max="13" width="15.85546875" style="7" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>22</v>
       </c>
       <c r="M2"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>22</v>
       </c>
       <c r="M3"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="I4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>22</v>
       </c>
       <c r="M4"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="I5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="M6"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="9" t="s">
+      <c r="H7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="J7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="K7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>22</v>
       </c>
       <c r="M7"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>22</v>
       </c>
       <c r="M8"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E10" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="M10"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="9" t="s">
+      <c r="H11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="J11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L9" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="K11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>22</v>
-      </c>
       <c r="M11"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="K12" s="8"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="K13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="K13" s="8"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="K14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="K14" s="8"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="K15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="K15" s="8"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="K16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="K16" s="8"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="K17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="K17" s="8"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="K18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="K18" s="8"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="K19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="K19" s="8"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="K20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="K20" s="8"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="K21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="K21" s="8"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="K22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="K22" s="8"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="K23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="K23" s="8"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="K24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="K24" s="8"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="K25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="K25" s="8"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="K26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="K26" s="8"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="K27" s="9"/>
+      <c r="B27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="K27" s="8"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="K28" s="9"/>
+      <c r="B28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="K28" s="8"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="K29" s="9"/>
+      <c r="B29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="K29" s="8"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="K30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="K30" s="8"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="K31" s="9"/>
+      <c r="B31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="K31" s="8"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="F32" s="9"/>
+      <c r="B32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="F32" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1090,153 +1136,342 @@
     <col min="4" max="4" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="14" t="s">
         <v>20</v>
       </c>
+      <c r="E1" s="14" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2">
-        <v>5</v>
+      <c r="A2" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="16">
+        <v>5</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="16">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="16">
+        <v>5</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="16">
+        <v>5</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
+      <c r="C5" s="16">
+        <v>5</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
+      <c r="B6" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="16">
+        <v>5</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="16">
+        <v>5</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="16">
+        <v>5</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="16">
+        <v>5</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
+      <c r="A10" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="18">
+        <v>5</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="18">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
+      <c r="A11" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="18">
+        <v>5</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="18">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="A12" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="18">
+        <v>5</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="18">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
+      <c r="A13" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="18">
+        <v>5</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
+      <c r="A14" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="18">
+        <v>5</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="18">
+        <v>10</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
+      <c r="A15" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="18">
+        <v>5</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="18">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
+      <c r="A16" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="18">
+        <v>5</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="18">
+        <v>5</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+      <c r="A17" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="18">
+        <v>5</v>
+      </c>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
+      <c r="A18" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="18">
+        <v>5</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="18">
+        <v>10</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="18">
+        <v>5</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="18">
+        <v>5</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="18">
+        <v>5</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="18">
+        <v>5</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
+      <c r="A21" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="18">
+        <v>5</v>
+      </c>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
